--- a/figures/source/Reviewed_articles_only.xlsx
+++ b/figures/source/Reviewed_articles_only.xlsx
@@ -18,9 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task_long" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="platforms_long" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="journals_long" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRISMA" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Studies'!$A$1:$Y$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'PRISMA'!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -20376,6 +20378,638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Web of Science</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Scopus</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Google Scholar Labs</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>In 2015-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Web of Science</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>In 2015-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Scopus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>In 2015-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>In 2015-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>In 2015-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Google Scholar Labs</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Web of Science</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scopus</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Google Scholar Labs</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Web of Science</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Scopus</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Google Scholar Labs</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Web of Science</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Scopus</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Google Scholar Labs</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IEEE Xplore by type</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Conference, returned</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IEEE Xplore by type</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Journal, returned</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IEEE Xplore by type</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Conference, in 2015-2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IEEE Xplore by type</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Journal, in 2015-2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Duplicates removed</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>All databases</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Excluded at screening</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Excluded at screening</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Global scope</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Excluded at screening</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Excluded at screening</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Outside Africa</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Full text unavailable</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Excluded at full text</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Off-theme</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Excluded at full text</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Insufficient depth</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Excluded at full text</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>No EO data</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Excluded at full text</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Publication type</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Excluded at full text</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/figures/source/Reviewed_articles_only.xlsx
+++ b/figures/source/Reviewed_articles_only.xlsx
@@ -22,7 +22,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Studies'!$A$1:$Y$139</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'PRISMA'!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y139"/>
+  <dimension ref="A1:AF139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -592,6 +591,41 @@
           <t>Resource last accessed</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Imagery access</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>n_institutions</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>inst_countries</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>collab_breadth</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>has_african_inst</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>african_leadership</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>cross_sector</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -667,6 +701,39 @@
       <c r="W2" s="1" t="n"/>
       <c r="X2" s="1" t="n"/>
       <c r="Y2" s="1" t="n"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -748,6 +815,39 @@
       <c r="W3" s="1" t="n"/>
       <c r="X3" s="1" t="n"/>
       <c r="Y3" s="1" t="n"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>AU; ZA</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -851,6 +951,39 @@
       <c r="W4" s="1" t="n"/>
       <c r="X4" s="1" t="n"/>
       <c r="Y4" s="1" t="n"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>BE; US; ZA</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -946,6 +1079,39 @@
       <c r="W5" s="1" t="n"/>
       <c r="X5" s="1" t="n"/>
       <c r="Y5" s="1" t="n"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>IN; US</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1035,6 +1201,39 @@
       <c r="Y6" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1120,6 +1319,39 @@
       <c r="W7" s="1" t="n"/>
       <c r="X7" s="1" t="n"/>
       <c r="Y7" s="1" t="n"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1199,6 +1431,39 @@
       <c r="W8" s="1" t="n"/>
       <c r="X8" s="1" t="n"/>
       <c r="Y8" s="1" t="n"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1298,6 +1563,39 @@
       <c r="W9" s="1" t="n"/>
       <c r="X9" s="1" t="n"/>
       <c r="Y9" s="1" t="n"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1402,6 +1700,39 @@
       <c r="X10" s="1" t="n"/>
       <c r="Y10" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>BE; DE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1482,6 +1813,39 @@
       <c r="W11" s="1" t="n"/>
       <c r="X11" s="1" t="n"/>
       <c r="Y11" s="1" t="n"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>DE; NL</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1565,6 +1929,39 @@
       <c r="W12" s="1" t="n"/>
       <c r="X12" s="1" t="n"/>
       <c r="Y12" s="1" t="n"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>CA; US</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1656,6 +2053,39 @@
       <c r="W13" s="1" t="n"/>
       <c r="X13" s="1" t="n"/>
       <c r="Y13" s="1" t="n"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>IN; NG</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1743,6 +2173,39 @@
       <c r="W14" s="1" t="n"/>
       <c r="X14" s="1" t="n"/>
       <c r="Y14" s="1" t="n"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>CA; US</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1832,6 +2295,39 @@
       <c r="Y15" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1923,6 +2419,39 @@
       <c r="W16" s="1" t="n"/>
       <c r="X16" s="1" t="n"/>
       <c r="Y16" s="1" t="n"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>NL; UG</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2002,6 +2531,39 @@
       <c r="W17" s="1" t="n"/>
       <c r="X17" s="1" t="n"/>
       <c r="Y17" s="1" t="n"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>US; ZA</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2081,6 +2643,39 @@
       <c r="W18" s="1" t="n"/>
       <c r="X18" s="1" t="n"/>
       <c r="Y18" s="1" t="n"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2177,6 +2772,39 @@
       <c r="X19" s="1" t="n"/>
       <c r="Y19" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>RW; US</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2249,6 +2877,39 @@
       <c r="W20" s="1" t="n"/>
       <c r="X20" s="1" t="n"/>
       <c r="Y20" s="1" t="n"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>KE; NL</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2338,6 +2999,39 @@
       <c r="Y21" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2445,6 +3139,39 @@
       <c r="W22" s="1" t="n"/>
       <c r="X22" s="1" t="n"/>
       <c r="Y22" s="1" t="n"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>CN; EG</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2553,6 +3280,39 @@
       <c r="X23" s="1" t="n"/>
       <c r="Y23" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2638,6 +3398,39 @@
       </c>
       <c r="Y24" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>BE; FR; GB; ID; IT; NL; ZA</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2714,6 +3507,39 @@
       <c r="W25" s="1" t="n"/>
       <c r="X25" s="1" t="n"/>
       <c r="Y25" s="1" t="n"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2797,6 +3623,39 @@
       <c r="W26" s="1" t="n"/>
       <c r="X26" s="1" t="n"/>
       <c r="Y26" s="1" t="n"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2880,6 +3739,39 @@
       <c r="W27" s="1" t="n"/>
       <c r="X27" s="1" t="n"/>
       <c r="Y27" s="1" t="n"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>CN; GB</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2969,6 +3861,39 @@
       <c r="Y28" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>NG; US</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3064,6 +3989,39 @@
       <c r="W29" s="1" t="n"/>
       <c r="X29" s="1" t="n"/>
       <c r="Y29" s="1" t="n"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3147,6 +4105,39 @@
       <c r="W30" s="1" t="n"/>
       <c r="X30" s="1" t="n"/>
       <c r="Y30" s="1" t="n"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3222,6 +4213,39 @@
       <c r="W31" s="1" t="n"/>
       <c r="X31" s="1" t="n"/>
       <c r="Y31" s="1" t="n"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3297,6 +4321,39 @@
       <c r="W32" s="1" t="n"/>
       <c r="X32" s="1" t="n"/>
       <c r="Y32" s="1" t="n"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>DE; KE; SD; ZA</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3385,6 +4442,39 @@
       </c>
       <c r="Y33" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>BE; BJ; CO; IT; US</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -3461,6 +4551,39 @@
       <c r="W34" s="1" t="n"/>
       <c r="X34" s="1" t="n"/>
       <c r="Y34" s="1" t="n"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>DE; KE; SD; ZW</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3556,6 +4679,39 @@
       <c r="W35" s="1" t="n"/>
       <c r="X35" s="1" t="n"/>
       <c r="Y35" s="1" t="n"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>DE; NG</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3655,6 +4811,39 @@
       <c r="W36" s="1" t="n"/>
       <c r="X36" s="1" t="n"/>
       <c r="Y36" s="1" t="n"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>DE; GH</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3738,6 +4927,39 @@
       <c r="W37" s="1" t="n"/>
       <c r="X37" s="1" t="n"/>
       <c r="Y37" s="1" t="n"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>KE; TZ; US</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3842,6 +5064,39 @@
       <c r="X38" s="1" t="n"/>
       <c r="Y38" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>CI; GB; KE; MX; RS; US</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3934,6 +5189,39 @@
       <c r="W39" s="1" t="n"/>
       <c r="X39" s="1" t="n"/>
       <c r="Y39" s="1" t="n"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4025,6 +5313,39 @@
       <c r="W40" s="1" t="n"/>
       <c r="X40" s="1" t="n"/>
       <c r="Y40" s="1" t="n"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4124,6 +5445,39 @@
       <c r="W41" s="1" t="n"/>
       <c r="X41" s="1" t="n"/>
       <c r="Y41" s="1" t="n"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>CN; KE; MX; US</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4211,6 +5565,39 @@
       <c r="W42" s="1" t="n"/>
       <c r="X42" s="1" t="n"/>
       <c r="Y42" s="1" t="n"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>KE; US</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4306,6 +5693,39 @@
       <c r="W43" s="1" t="n"/>
       <c r="X43" s="1" t="n"/>
       <c r="Y43" s="1" t="n"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>BF; SE</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4405,6 +5825,39 @@
       <c r="W44" s="1" t="n"/>
       <c r="X44" s="1" t="n"/>
       <c r="Y44" s="1" t="n"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>CN; DE; EE; GB; IN; US</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4484,6 +5937,39 @@
       <c r="W45" s="1" t="n"/>
       <c r="X45" s="1" t="n"/>
       <c r="Y45" s="1" t="n"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4559,6 +6045,39 @@
       <c r="W46" s="1" t="n"/>
       <c r="X46" s="1" t="n"/>
       <c r="Y46" s="1" t="n"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>FR; MZ</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4651,6 +6170,39 @@
       </c>
       <c r="Y47" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>DE; FR; NL</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4731,6 +6283,39 @@
       <c r="W48" s="1" t="n"/>
       <c r="X48" s="1" t="n"/>
       <c r="Y48" s="1" t="n"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>AU; ES; FR; GB; IT; NL; ZA</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4835,6 +6420,39 @@
       <c r="X49" s="1" t="n"/>
       <c r="Y49" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>CA; GB; IT</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4925,6 +6543,39 @@
       <c r="Y50" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>GB; MA; US</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5022,6 +6673,39 @@
       <c r="Y51" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5130,6 +6814,39 @@
       <c r="X52" s="1" t="n"/>
       <c r="Y52" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>CN; EG</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -5226,6 +6943,39 @@
       <c r="W53" s="1" t="n"/>
       <c r="X53" s="1" t="n"/>
       <c r="Y53" s="1" t="n"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5317,6 +7067,39 @@
       <c r="W54" s="1" t="n"/>
       <c r="X54" s="1" t="n"/>
       <c r="Y54" s="1" t="n"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>DE; ZA</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5400,6 +7183,39 @@
       <c r="W55" s="1" t="n"/>
       <c r="X55" s="1" t="n"/>
       <c r="Y55" s="1" t="n"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>KE; TZ</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5491,6 +7307,39 @@
       <c r="W56" s="1" t="n"/>
       <c r="X56" s="1" t="n"/>
       <c r="Y56" s="1" t="n"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5574,6 +7423,39 @@
       <c r="W57" s="1" t="n"/>
       <c r="X57" s="1" t="n"/>
       <c r="Y57" s="1" t="n"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5669,6 +7551,39 @@
       <c r="W58" s="1" t="n"/>
       <c r="X58" s="1" t="n"/>
       <c r="Y58" s="1" t="n"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5756,6 +7671,39 @@
       <c r="W59" s="1" t="n"/>
       <c r="X59" s="1" t="n"/>
       <c r="Y59" s="1" t="n"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>JP; LK; ZM</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5835,6 +7783,39 @@
       <c r="W60" s="1" t="n"/>
       <c r="X60" s="1" t="n"/>
       <c r="Y60" s="1" t="n"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>CA; PL</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5918,6 +7899,39 @@
       <c r="W61" s="1" t="n"/>
       <c r="X61" s="1" t="n"/>
       <c r="Y61" s="1" t="n"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5997,6 +8011,39 @@
       <c r="W62" s="1" t="n"/>
       <c r="X62" s="1" t="n"/>
       <c r="Y62" s="1" t="n"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>AT; IT</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -6088,6 +8135,39 @@
       <c r="W63" s="1" t="n"/>
       <c r="X63" s="1" t="n"/>
       <c r="Y63" s="1" t="n"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ET; ZA</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -6179,6 +8259,39 @@
       <c r="W64" s="1" t="n"/>
       <c r="X64" s="1" t="n"/>
       <c r="Y64" s="1" t="n"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -6256,6 +8369,39 @@
       <c r="W65" s="1" t="n"/>
       <c r="X65" s="1" t="n"/>
       <c r="Y65" s="1" t="n"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -6343,6 +8489,39 @@
       <c r="W66" s="1" t="n"/>
       <c r="X66" s="1" t="n"/>
       <c r="Y66" s="1" t="n"/>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ET; ZA</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -6446,6 +8625,39 @@
       <c r="W67" s="1" t="n"/>
       <c r="X67" s="1" t="n"/>
       <c r="Y67" s="1" t="n"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -6549,6 +8761,39 @@
       <c r="W68" s="1" t="n"/>
       <c r="X68" s="1" t="n"/>
       <c r="Y68" s="1" t="n"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -6644,6 +8889,39 @@
       <c r="W69" s="1" t="n"/>
       <c r="X69" s="1" t="n"/>
       <c r="Y69" s="1" t="n"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA69" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -6737,6 +9015,39 @@
       <c r="Y70" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA70" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>FR; IN; SN</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6824,6 +9135,39 @@
       <c r="W71" s="1" t="n"/>
       <c r="X71" s="1" t="n"/>
       <c r="Y71" s="1" t="n"/>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>CN; HK</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6932,6 +9276,39 @@
       <c r="X72" s="1" t="n"/>
       <c r="Y72" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>CL; GB; IT; US</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -7024,6 +9401,39 @@
       <c r="W73" s="1" t="n"/>
       <c r="X73" s="1" t="n"/>
       <c r="Y73" s="1" t="n"/>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>EG; US</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -7111,6 +9521,39 @@
       <c r="W74" s="1" t="n"/>
       <c r="X74" s="1" t="n"/>
       <c r="Y74" s="1" t="n"/>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -7210,6 +9653,39 @@
       <c r="W75" s="1" t="n"/>
       <c r="X75" s="1" t="n"/>
       <c r="Y75" s="1" t="n"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>DZ; IT; TN; US</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -7293,6 +9769,39 @@
       <c r="W76" s="1" t="n"/>
       <c r="X76" s="1" t="n"/>
       <c r="Y76" s="1" t="n"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>CN; GB</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -7378,6 +9887,39 @@
       <c r="Y77" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -7465,6 +10007,39 @@
       <c r="Y78" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA78" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>DE; ES; FR; GB; IT</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -7566,6 +10141,39 @@
       <c r="Y79" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>CH; ES</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -7669,6 +10277,39 @@
       <c r="W80" s="1" t="n"/>
       <c r="X80" s="1" t="n"/>
       <c r="Y80" s="1" t="n"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -7760,6 +10401,39 @@
       <c r="W81" s="1" t="n"/>
       <c r="X81" s="1" t="n"/>
       <c r="Y81" s="1" t="n"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>MZ; PT</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -7847,6 +10521,39 @@
       <c r="W82" s="1" t="n"/>
       <c r="X82" s="1" t="n"/>
       <c r="Y82" s="1" t="n"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -7946,6 +10653,39 @@
       <c r="W83" s="1" t="n"/>
       <c r="X83" s="1" t="n"/>
       <c r="Y83" s="1" t="n"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA83" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>CI; DE; FR; US</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -8037,6 +10777,39 @@
       <c r="W84" s="1" t="n"/>
       <c r="X84" s="1" t="n"/>
       <c r="Y84" s="1" t="n"/>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>GB; IT; US</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -8132,6 +10905,39 @@
       <c r="W85" s="1" t="n"/>
       <c r="X85" s="1" t="n"/>
       <c r="Y85" s="1" t="n"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -8232,6 +11038,39 @@
       <c r="X86" s="1" t="n"/>
       <c r="Y86" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>AE; MA; US</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -8320,6 +11159,39 @@
       <c r="W87" s="1" t="n"/>
       <c r="X87" s="1" t="n"/>
       <c r="Y87" s="1" t="n"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>ET; ZA</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -8419,6 +11291,39 @@
       <c r="W88" s="1" t="n"/>
       <c r="X88" s="1" t="n"/>
       <c r="Y88" s="1" t="n"/>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -8508,6 +11413,39 @@
       <c r="Y89" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>DE; ES</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -8611,6 +11549,39 @@
       <c r="W90" s="1" t="n"/>
       <c r="X90" s="1" t="n"/>
       <c r="Y90" s="1" t="n"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>NG; US</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -8706,6 +11677,39 @@
       <c r="W91" s="1" t="n"/>
       <c r="X91" s="1" t="n"/>
       <c r="Y91" s="1" t="n"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA91" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -8799,6 +11803,39 @@
       <c r="W92" s="1" t="n"/>
       <c r="X92" s="1" t="n"/>
       <c r="Y92" s="1" t="n"/>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -8899,6 +11936,39 @@
       <c r="X93" s="1" t="n"/>
       <c r="Y93" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -8995,6 +12065,39 @@
       <c r="W94" s="1" t="n"/>
       <c r="X94" s="1" t="n"/>
       <c r="Y94" s="1" t="n"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA94" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>BE; CH; GB; KE; TZ</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -9082,6 +12185,39 @@
       <c r="W95" s="1" t="n"/>
       <c r="X95" s="1" t="n"/>
       <c r="Y95" s="1" t="n"/>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>GB; ZM</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -9177,6 +12313,39 @@
       <c r="W96" s="1" t="n"/>
       <c r="X96" s="1" t="n"/>
       <c r="Y96" s="1" t="n"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA96" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>AR; BE; DE; GB; KE; US</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -9272,6 +12441,39 @@
       <c r="W97" s="1" t="n"/>
       <c r="X97" s="1" t="n"/>
       <c r="Y97" s="1" t="n"/>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA97" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>BF; CI; GB; PE; US</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -9353,6 +12555,39 @@
       <c r="Y98" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA98" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>IT; SN; US; ZA</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -9432,6 +12667,39 @@
       <c r="W99" s="1" t="n"/>
       <c r="X99" s="1" t="n"/>
       <c r="Y99" s="1" t="n"/>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>BJ; DE; GH; TG</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -9507,6 +12775,39 @@
       <c r="W100" s="1" t="n"/>
       <c r="X100" s="1" t="n"/>
       <c r="Y100" s="1" t="n"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -9607,6 +12908,39 @@
       <c r="X101" s="1" t="n"/>
       <c r="Y101" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA101" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>FR; IT; KE; ZA</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -9679,6 +13013,39 @@
       <c r="W102" s="1" t="n"/>
       <c r="X102" s="1" t="n"/>
       <c r="Y102" s="1" t="n"/>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>GB; RW; US</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -9764,6 +13131,39 @@
       <c r="W103" s="1" t="n"/>
       <c r="X103" s="1" t="n"/>
       <c r="Y103" s="1" t="n"/>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -9845,6 +13245,39 @@
       <c r="Y104" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA104" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>CZ; DE; GB; PL</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -9930,6 +13363,39 @@
       <c r="Y105" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA105" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>BE; ES; NL; SE</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -10013,6 +13479,39 @@
       <c r="W106" s="1" t="n"/>
       <c r="X106" s="1" t="n"/>
       <c r="Y106" s="1" t="n"/>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -10092,6 +13591,39 @@
       <c r="W107" s="1" t="n"/>
       <c r="X107" s="1" t="n"/>
       <c r="Y107" s="1" t="n"/>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>NL; US</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -10175,6 +13707,39 @@
       <c r="W108" s="1" t="n"/>
       <c r="X108" s="1" t="n"/>
       <c r="Y108" s="1" t="n"/>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -10258,6 +13823,39 @@
       </c>
       <c r="X109" s="1" t="n"/>
       <c r="Y109" s="1" t="n"/>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>CH; GB</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -10339,6 +13937,39 @@
       <c r="Y110" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>DE; KR</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -10434,6 +14065,39 @@
       <c r="W111" s="1" t="n"/>
       <c r="X111" s="1" t="n"/>
       <c r="Y111" s="1" t="n"/>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -10513,6 +14177,39 @@
       <c r="W112" s="1" t="n"/>
       <c r="X112" s="1" t="n"/>
       <c r="Y112" s="1" t="n"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>AU; NG</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -10588,6 +14285,39 @@
       <c r="W113" s="1" t="n"/>
       <c r="X113" s="1" t="n"/>
       <c r="Y113" s="1" t="n"/>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -10667,6 +14397,39 @@
       <c r="W114" s="1" t="n"/>
       <c r="X114" s="1" t="n"/>
       <c r="Y114" s="1" t="n"/>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -10746,6 +14509,39 @@
       <c r="W115" s="1" t="n"/>
       <c r="X115" s="1" t="n"/>
       <c r="Y115" s="1" t="n"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>GH; ZA</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -10829,6 +14625,39 @@
       <c r="W116" s="1" t="n"/>
       <c r="X116" s="1" t="n"/>
       <c r="Y116" s="1" t="n"/>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -10912,6 +14741,39 @@
       <c r="W117" s="1" t="n"/>
       <c r="X117" s="1" t="n"/>
       <c r="Y117" s="1" t="n"/>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>BE; NL; SE</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -11002,6 +14864,39 @@
       <c r="X118" s="1" t="n"/>
       <c r="Y118" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -11074,6 +14969,39 @@
       <c r="W119" s="1" t="n"/>
       <c r="X119" s="1" t="n"/>
       <c r="Y119" s="1" t="n"/>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>AT; CN; DE</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -11149,6 +15077,39 @@
       <c r="W120" s="1" t="n"/>
       <c r="X120" s="1" t="n"/>
       <c r="Y120" s="1" t="n"/>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -11220,6 +15181,39 @@
       <c r="W121" s="1" t="n"/>
       <c r="X121" s="1" t="n"/>
       <c r="Y121" s="1" t="n"/>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>GB; RW; US</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -11299,6 +15293,39 @@
       <c r="W122" s="1" t="n"/>
       <c r="X122" s="1" t="n"/>
       <c r="Y122" s="1" t="n"/>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -11403,6 +15430,39 @@
       <c r="X123" s="1" t="n"/>
       <c r="Y123" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AA123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>CA; CH; DE; NL; US</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -11487,6 +15547,39 @@
       <c r="W124" s="1" t="n"/>
       <c r="X124" s="1" t="n"/>
       <c r="Y124" s="1" t="n"/>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Multi-institution, single-country</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -11587,6 +15680,39 @@
       </c>
       <c r="Y125" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>SE; US</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -11667,6 +15793,39 @@
       <c r="W126" s="1" t="n"/>
       <c r="X126" s="1" t="n"/>
       <c r="Y126" s="1" t="n"/>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -11754,6 +15913,39 @@
       <c r="W127" s="1" t="n"/>
       <c r="X127" s="1" t="n"/>
       <c r="Y127" s="1" t="n"/>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>BE; IT; NL; US</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -11853,6 +16045,39 @@
       <c r="W128" s="1" t="n"/>
       <c r="X128" s="1" t="n"/>
       <c r="Y128" s="1" t="n"/>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA128" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>CN; NG</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -11953,6 +16178,39 @@
       <c r="X129" s="1" t="n"/>
       <c r="Y129" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -12037,6 +16295,39 @@
       <c r="W130" s="1" t="n"/>
       <c r="X130" s="1" t="n"/>
       <c r="Y130" s="1" t="n"/>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>BW; US</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -12120,6 +16411,39 @@
       <c r="W131" s="1" t="n"/>
       <c r="X131" s="1" t="n"/>
       <c r="Y131" s="1" t="n"/>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>DE; GH; NE; NG</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -12203,6 +16527,39 @@
       <c r="W132" s="1" t="n"/>
       <c r="X132" s="1" t="n"/>
       <c r="Y132" s="1" t="n"/>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>African-only</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -12288,6 +16645,39 @@
       <c r="Y133" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA133" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>CA; GB; GH; US</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -12377,6 +16767,39 @@
       <c r="Y134" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="AA134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>GB; GH; RW</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -12464,6 +16887,39 @@
       <c r="W135" s="1" t="n"/>
       <c r="X135" s="1" t="n"/>
       <c r="Y135" s="1" t="n"/>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -12555,6 +17011,39 @@
       <c r="W136" s="1" t="n"/>
       <c r="X136" s="1" t="n"/>
       <c r="Y136" s="1" t="n"/>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>DE; NG</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -12663,6 +17152,39 @@
       <c r="X137" s="1" t="n"/>
       <c r="Y137" s="4" t="n">
         <v>46266</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>BE; DZ; JP; SA</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>North-South</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -12743,6 +17265,39 @@
       <c r="W138" s="1" t="n"/>
       <c r="X138" s="1" t="n"/>
       <c r="Y138" s="1" t="n"/>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>Non-satellite</t>
+        </is>
+      </c>
+      <c r="AA138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>DE; PL</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Multi-country</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -12826,6 +17381,39 @@
       <c r="W139" s="1" t="n"/>
       <c r="X139" s="1" t="n"/>
       <c r="Y139" s="1" t="n"/>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="AA139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Single-institution</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>Non-African-only</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Y139"/>
@@ -20862,11 +25450,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Out of scope</t>
+          <t>Globalscope</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -20877,11 +25465,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Global scope</t>
+          <t>Outofscope</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -20892,11 +25480,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>OutsideAfrica</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -20907,11 +25495,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Outside Africa</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -20937,11 +25525,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Off-theme</t>
+          <t>Insufficientdepth</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
@@ -20952,11 +25540,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Insufficient depth</t>
+          <t>NoEOdata</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -20967,11 +25555,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>No EO data</t>
+          <t>Offtheme</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
@@ -20982,7 +25570,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Publication type</t>
+          <t>Publicationtype</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -21005,7 +25593,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39565,6 +44152,11 @@
           <t>Nature Communications</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>Continental</t>
